--- a/test_ai/测试用例_罗盛哲.xlsx
+++ b/test_ai/测试用例_罗盛哲.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="161">
   <si>
     <t>在此处概述本测试用例</t>
   </si>
@@ -1525,6 +1525,126 @@
   <si>
     <t xml:space="preserve">A/B算法对比（9种算法×6条用例全量扫描）+ 指标断言（Hit@1）+ 回答依据校验；依据校验的锚点为ST-AI-RAG-006的Agent回答。</t>
   </si>
+  <si>
+    <t xml:space="preserve">ST-AI-RAG-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库检索与回答依据：回答依据留痕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每条回答都留下知识库工具调用记录与可核验依据，不得脱离知识库自由发挥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对 ST-AI-RAG-001、ST-AI-RAG-002、ST-AI-RAG-003、ST-AI-RAG-006 四道政策问题分别取 Agent 回答，逐条校验回答依据。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逐个向已发布Agent发送上述四个政策问题并取回回答；对每条回答检查是否出现knowledge_base_search工具调用记录，以及是否出现至少一处可核验依据（书名号政策名/发文字号/知识库或检索表述）；测试结束后删除会话。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">四条回答全部通过依据校验：均含知识库工具调用记录，且均出现可核验的政策依据痕迹。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSED：四条回答均通过依据校验，未出现脱离知识库自由发挥的回答。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回答依据校验（工具调用留痕＋依据痕迹双证据）；校验范围限定为已实测确认的4条回答，004为预期失败用例、005的回答未做依据校验，故不纳入。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-AI-RAG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库检索：检索接口契约（Top-K与排序）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">检索接口遵守Top-K上限、按分数降序返回，且命中项字段完整</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以 ST-AI-RAG-001 的政策问题检索Top-5（默认算法）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以该问题调用知识库检索接口（默认算法、Top-5）；核对按documentId去重后的文档条数是否不超过Top-K；逐条检查命中项是否含documentId与title；核对返回片段的分值序列是否单调不增。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">去重后文档条数≤5；每条命中项均含documentId与title；分值序列单调不增。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSED：返回条数未超Top-K，命中项字段完整，分值序列保持降序（单调不增）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接口契约测试（Top-K边界值＋排序不变量＋字段完整性）；这三条是Hit@K、MRR、nDCG等指标算得对的前提。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-AI-RAG-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库检索：检索接口契约（最低分数阈值）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">低于最低分数(minScore)的片段不得进入检索结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以 ST-AI-RAG-001 的政策问题检索Top-5，minScore=0.2。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以该问题调用知识库检索接口（默认算法、Top-5、minScore=0.2）；逐条核对返回片段的score是否均不低于0.2（保留1e-6浮点容差）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全部返回片段的score均≥0.2，无低分噪声片段混入结果。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSED：全部返回片段的score均不低于0.2，最低分数阈值生效。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接口契约测试（阈值过滤）；仅校验默认算法——weighted/hybrid等重排类算法返回的是重排分数，量纲与传统相似度不同，不适用同一阈值。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-AI-RAG-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库检索：检索范围隔离</t>
+  </si>
+  <si>
+    <t xml:space="preserve">检索结果只能来自Agent绑定的那一个知识库，不得越界到其他知识库</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以 ST-AI-RAG-001 的政策问题检索Top-5，kbIds仅指定Agent绑定的政策知识库。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以该问题调用知识库检索接口（kbIds指定为绑定的政策知识库、Top-5）；逐条核对返回片段所属的kbId是否与绑定知识库ID一致。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全部返回片段的kbId均等于Agent绑定的知识库ID，无跨库召回的片段。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSED：全部返回片段均来自绑定的政策知识库，未出现越界片段。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接口契约测试（多知识库隔离）；防止跨库召回污染回答依据，保证依据可溯源到指定知识库。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-AI-RAG-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库检索：Top-K结果去重</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同一篇文档在Top-K里只能占据一个名次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6条政策问题 × 9种已注册检索算法的检索结果，共54组Top-5。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对全部6条政策问题分别用9种已注册检索算法各检索一次Top-5（请求间隔1.3s以规避限流）；逐组核对Top-K内是否存在同一documentId占据多个名次。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54组检索结果的Top-K内均无重复文档，同一文档只占一个名次。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSED：全部检索算法×用例组合的Top-K内均无重复文档。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接口契约测试（结果去重）；同一文档的多个切片占满名次会挤掉其他候选文档，直接影响召回多样性，本条同时守住去重逻辑未被改坏。</t>
+  </si>
 </sst>
 </file>
 
@@ -3812,84 +3932,214 @@
       </c>
       <c r="N6" s="43"/>
     </row>
-    <row r="7" spans="1:140" x14ac:dyDescent="0.3">
-      <c r="A7" s="42"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
+    <row r="7" ht="65" spans="1:140" x14ac:dyDescent="0.3">
+      <c r="A7" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="J7" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="K7" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="L7" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="42" t="s">
+        <v>128</v>
+      </c>
       <c r="N7" s="43"/>
     </row>
-    <row r="8" spans="1:140" x14ac:dyDescent="0.3">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+    <row r="8" ht="65" spans="1:140" x14ac:dyDescent="0.3">
+      <c r="A8" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="L8" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="42" t="s">
+        <v>136</v>
+      </c>
       <c r="N8" s="43"/>
     </row>
-    <row r="9" spans="1:140" x14ac:dyDescent="0.3">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
+    <row r="9" ht="65" spans="1:140" x14ac:dyDescent="0.3">
+      <c r="A9" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="J9" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="K9" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="42" t="s">
+        <v>144</v>
+      </c>
       <c r="N9" s="43"/>
     </row>
-    <row r="10" spans="1:140" x14ac:dyDescent="0.3">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
+    <row r="10" ht="65" spans="1:140" x14ac:dyDescent="0.3">
+      <c r="A10" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="J10" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="L10" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="42" t="s">
+        <v>152</v>
+      </c>
       <c r="N10" s="43"/>
     </row>
-    <row r="11" spans="1:140" x14ac:dyDescent="0.3">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
+    <row r="11" ht="65" spans="1:140" x14ac:dyDescent="0.3">
+      <c r="A11" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="J11" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="K11" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="L11" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="42" t="s">
+        <v>160</v>
+      </c>
       <c r="N11" s="43"/>
     </row>
     <row r="12" spans="1:140" x14ac:dyDescent="0.3">
